--- a/Standard_Chart_Template.xlsx
+++ b/Standard_Chart_Template.xlsx
@@ -16,6 +16,7 @@
     <sheet name="EjectorGuidePin" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="EjectorGuideBush" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="LocatingRing" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="PlateThickness" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -473,6 +474,30 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Thickness</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Standard_Chart_Template.xlsx
+++ b/Standard_Chart_Template.xlsx
@@ -17,6 +17,7 @@
     <sheet name="EjectorGuideBush" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="LocatingRing" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="PlateThickness" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Cavityhousingdrilling" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,6 +499,42 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Thickness</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Standard_Chart_Template.xlsx
+++ b/Standard_Chart_Template.xlsx
@@ -18,6 +18,8 @@
     <sheet name="LocatingRing" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="PlateThickness" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Cavityhousingdrilling" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="BoltStandards" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="SpacerBlocksCosting" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -535,6 +537,78 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bolt Dia</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Clearance hole dia</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Counter bore dia</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Counter bore depth</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Thickness</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -678,7 +752,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>Outer dia</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/Standard_Chart_Template.xlsx
+++ b/Standard_Chart_Template.xlsx
@@ -20,6 +20,8 @@
     <sheet name="Cavityhousingdrilling" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="BoltStandards" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="SpacerBlocksCosting" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="PunchHousingDrilling" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="PunchBackPlate" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -609,6 +611,78 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Thickness</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Thickness</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
